--- a/data/trans_bre/P38B-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P38B-Habitat-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 7,26</t>
+          <t>-0,38; 7,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 7,9</t>
+          <t>0,56; 8,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 10,78</t>
+          <t>1,92; 10,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 8,88</t>
+          <t>-0,44; 8,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 9,77</t>
+          <t>0,66; 9,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 13,04</t>
+          <t>2,11; 13,19</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 8,38</t>
+          <t>1,65; 8,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,54; 11,49</t>
+          <t>5,34; 11,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,61; 51,92</t>
+          <t>5,46; 51,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 10,57</t>
+          <t>2,05; 10,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,62; 14,49</t>
+          <t>6,39; 14,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,26; 155,96</t>
+          <t>7,04; 155,4</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 10,33</t>
+          <t>3,15; 10,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 10,62</t>
+          <t>3,03; 10,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,08; 17,28</t>
+          <t>4,79; 17,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,16; 12,71</t>
+          <t>3,71; 13,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 13,4</t>
+          <t>3,61; 13,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,25; 22,8</t>
+          <t>5,82; 23,29</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,67; 10,13</t>
+          <t>3,59; 10,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 5,76</t>
+          <t>-1,25; 5,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 8,13</t>
+          <t>-15,69; 8,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 12,8</t>
+          <t>4,29; 12,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 7,24</t>
+          <t>-1,51; 7,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,07; 10,21</t>
+          <t>-18,78; 10,4</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,96; 7,34</t>
+          <t>3,8; 7,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 7,27</t>
+          <t>3,76; 7,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,37; 31,2</t>
+          <t>4,51; 27,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,75; 9,03</t>
+          <t>4,6; 9,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,59; 9,01</t>
+          <t>4,55; 9,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,38; 54,37</t>
+          <t>5,51; 46,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P38B-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P38B-Habitat-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,44</t>
+          <t>4,98</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 7,07</t>
+          <t>-0,31; 7,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 8,1</t>
+          <t>0,47; 7,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 10,89</t>
+          <t>1,23; 9,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 8,74</t>
+          <t>-0,33; 8,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 9,98</t>
+          <t>0,57; 9,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 13,19</t>
+          <t>1,39; 11,42</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22,81</t>
+          <t>7,13</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 8,36</t>
+          <t>1,67; 8,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,34; 11,55</t>
+          <t>5,56; 11,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 51,93</t>
+          <t>3,62; 11,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 10,55</t>
+          <t>2,06; 10,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,39; 14,36</t>
+          <t>6,58; 14,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,04; 155,4</t>
+          <t>4,5; 14,77</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9,93</t>
+          <t>7,63</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 10,77</t>
+          <t>3,68; 10,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 10,47</t>
+          <t>2,92; 10,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,79; 17,56</t>
+          <t>3,0; 12,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 13,46</t>
+          <t>4,31; 13,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 13,18</t>
+          <t>3,46; 13,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,82; 23,29</t>
+          <t>3,69; 16,7</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>6,81</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,59; 10,28</t>
+          <t>3,49; 9,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 5,64</t>
+          <t>-1,26; 5,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 8,25</t>
+          <t>2,99; 10,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,29; 12,91</t>
+          <t>4,2; 12,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 7,1</t>
+          <t>-1,51; 7,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 10,4</t>
+          <t>3,64; 13,86</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11,37</t>
+          <t>6,75</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,8; 7,3</t>
+          <t>3,96; 7,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 7,3</t>
+          <t>3,63; 7,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,51; 27,68</t>
+          <t>4,71; 8,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 9,02</t>
+          <t>4,79; 9,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,55; 9,04</t>
+          <t>4,4; 9,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,51; 46,01</t>
+          <t>5,77; 11,06</t>
         </is>
       </c>
     </row>
